--- a/payment_forms/035_customer_bill_pay--payment_forms.xlsx
+++ b/payment_forms/035_customer_bill_pay--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card',_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Card', 'value': 'credit_card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer',_'value':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Bank Transfer', 'value': 'bank_transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'ak',_'value':_'ak'}</t>
+          <t>ak</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'AK', 'value': 'AK'}</t>
+          <t>AK</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'al',_'value':_'al'}</t>
+          <t>al</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'AL', 'value': 'AL'}</t>
+          <t>AL</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'ar',_'value':_'ar'}</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'AR', 'value': 'AR'}</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'az',_'value':_'az'}</t>
+          <t>az</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'AZ', 'value': 'AZ'}</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'ca',_'value':_'ca'}</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'CA', 'value': 'CA'}</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'co',_'value':_'co'}</t>
+          <t>co</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'CO', 'value': 'CO'}</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'ct',_'value':_'ct'}</t>
+          <t>ct</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'CT', 'value': 'CT'}</t>
+          <t>CT</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'dc',_'value':_'dc'}</t>
+          <t>dc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'DC', 'value': 'DC'}</t>
+          <t>DC</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'de',_'value':_'de'}</t>
+          <t>de</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'DE', 'value': 'DE'}</t>
+          <t>DE</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'fl',_'value':_'fl'}</t>
+          <t>fl</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'FL', 'value': 'FL'}</t>
+          <t>FL</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'ga',_'value':_'ga'}</t>
+          <t>ga</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'GA', 'value': 'GA'}</t>
+          <t>GA</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'hi',_'value':_'hi'}</t>
+          <t>hi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'HI', 'value': 'HI'}</t>
+          <t>HI</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'id',_'value':_'id'}</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'ID', 'value': 'ID'}</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'il',_'value':_'il'}</t>
+          <t>il</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'IL', 'value': 'IL'}</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'in',_'value':_'in'}</t>
+          <t>in</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'IN', 'value': 'IN'}</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'ia',_'value':_'ia'}</t>
+          <t>ia</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'IA', 'value': 'IA'}</t>
+          <t>IA</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'ks',_'value':_'ks'}</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'KS', 'value': 'KS'}</t>
+          <t>KS</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'ky',_'value':_'ky'}</t>
+          <t>ky</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'KY', 'value': 'KY'}</t>
+          <t>KY</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'la',_'value':_'la'}</t>
+          <t>la</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'LA', 'value': 'LA'}</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'ma',_'value':_'ma'}</t>
+          <t>ma</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'MA', 'value': 'MA'}</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'md',_'value':_'md'}</t>
+          <t>md</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'MD', 'value': 'MD'}</t>
+          <t>MD</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'me',_'value':_'me'}</t>
+          <t>me</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'ME', 'value': 'ME'}</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'mi',_'value':_'mi'}</t>
+          <t>mi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'MI', 'value': 'MI'}</t>
+          <t>MI</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'mn',_'value':_'mn'}</t>
+          <t>mn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'MN', 'value': 'MN'}</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'mo',_'value':_'mo'}</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'MO', 'value': 'MO'}</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'ms',_'value':_'ms'}</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'MS', 'value': 'MS'}</t>
+          <t>MS</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'mt',_'value':_'mt'}</t>
+          <t>mt</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'MT', 'value': 'MT'}</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'nc',_'value':_'nc'}</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'NC', 'value': 'NC'}</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'nd',_'value':_'nd'}</t>
+          <t>nd</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'ND', 'value': 'ND'}</t>
+          <t>ND</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'ne',_'value':_'ne'}</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'NE', 'value': 'NE'}</t>
+          <t>NE</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'nh',_'value':_'nh'}</t>
+          <t>nh</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'NH', 'value': 'NH'}</t>
+          <t>NH</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'nj',_'value':_'nj'}</t>
+          <t>nj</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'NJ', 'value': 'NJ'}</t>
+          <t>NJ</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'nm',_'value':_'nm'}</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'NM', 'value': 'NM'}</t>
+          <t>NM</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'nv',_'value':_'nv'}</t>
+          <t>nv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'NV', 'value': 'NV'}</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'ny',_'value':_'ny'}</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'NY', 'value': 'NY'}</t>
+          <t>NY</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'oh',_'value':_'oh'}</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'OH', 'value': 'OH'}</t>
+          <t>OH</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'ok',_'value':_'ok'}</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'OK', 'value': 'OK'}</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'or',_'value':_'or'}</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'OR', 'value': 'OR'}</t>
+          <t>OR</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'pa',_'value':_'pa'}</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'PA', 'value': 'PA'}</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'ri',_'value':_'ri'}</t>
+          <t>ri</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'RI', 'value': 'RI'}</t>
+          <t>RI</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'sc',_'value':_'sc'}</t>
+          <t>sc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'SC', 'value': 'SC'}</t>
+          <t>SC</t>
         </is>
       </c>
     </row>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'sd',_'value':_'sd'}</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'SD', 'value': 'SD'}</t>
+          <t>SD</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'tn',_'value':_'tn'}</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'TN', 'value': 'TN'}</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'tx',_'value':_'tx'}</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'TX', 'value': 'TX'}</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'ut',_'value':_'ut'}</t>
+          <t>ut</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'UT', 'value': 'UT'}</t>
+          <t>UT</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1671,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'va',_'value':_'va'}</t>
+          <t>va</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'VA', 'value': 'VA'}</t>
+          <t>VA</t>
         </is>
       </c>
     </row>
@@ -1688,12 +1688,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'vt',_'value':_'vt'}</t>
+          <t>vt</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'VT', 'value': 'VT'}</t>
+          <t>VT</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1705,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'wa',_'value':_'wa'}</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'WA', 'value': 'WA'}</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'wi',_'value':_'wi'}</t>
+          <t>wi</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'WI', 'value': 'WI'}</t>
+          <t>WI</t>
         </is>
       </c>
     </row>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'wv',_'value':_'wv'}</t>
+          <t>wv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'WV', 'value': 'WV'}</t>
+          <t>WV</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'wy',_'value':_'wy'}</t>
+          <t>wy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'WY', 'value': 'WY'}</t>
+          <t>WY</t>
         </is>
       </c>
     </row>
